--- a/example.xlsx
+++ b/example.xlsx
@@ -2,27 +2,46 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
+      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="204"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="204"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="204"/>
+      <family val="0"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,16 +61,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -124,161 +159,97 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="44546a"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="e7e6e6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="5b9bd5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="ed7d31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="a5a5a5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="ffc000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4472c4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="70ad47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0563c1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="954f72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -286,33 +257,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -325,13 +287,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -341,15 +297,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -357,7 +311,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -365,2316 +318,2708 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F194"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="58.01" customWidth="1" style="1" min="5" max="5"/>
+    <col width="39.51" customWidth="1" style="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Название</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Начало</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Конец</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>url</t>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Участники</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Q177109</t>
+          <t>Q1503611</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Slovak–Hungarian War</t>
+          <t>Numantine War</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1939-03-23T00:00:00Z</t>
+          <t>-0142-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1939-04-04T00:00:00Z</t>
+          <t>-0132-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q177109</t>
+          <t>http://www.wikidata.org/entity/Q1503611</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Roman Republic, Kingdom of Numidia, Numantia, Vettones, Vaccaei, Arevaci, Lusones</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Q29122</t>
+          <t>Q1151705</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>First Anglo-Burmese War</t>
+          <t>Chu–Han Contention</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1824-03-05T00:00:00Z</t>
+          <t>-0205-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1826-02-24T00:00:00Z</t>
+          <t>-0201-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q29122</t>
+          <t>http://www.wikidata.org/entity/Q1151705</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Q29242</t>
+          <t>Q1230787</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Georgian–Ossetian conflict</t>
+          <t>First Celtiberian War</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1989-11-10T00:00:00Z</t>
+          <t>-0180-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>-0178-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q29242</t>
+          <t>http://www.wikidata.org/entity/Q1230787</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ancient Rome, Vaccaei, Celtiberians</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Q190029</t>
+          <t>Q1265861</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kosovo War</t>
+          <t>Great Illyrian Revolt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1998-02-27T00:00:00Z</t>
+          <t>0006-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1999-06-11T00:00:00Z</t>
+          <t>0009-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q190029</t>
+          <t>http://www.wikidata.org/entity/Q1265861</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Q184637</t>
+          <t>Q1123592</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ten Years' War</t>
+          <t>Cisalpine Gaul War</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1868-10-10T00:00:00Z</t>
+          <t>-0224-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1878-01-01T00:00:00Z</t>
+          <t>-0221-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q184637</t>
+          <t>http://www.wikidata.org/entity/Q1123592</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Q190758</t>
+          <t>Q1418062</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>War in Darfur</t>
+          <t>Fourth Syrian War</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2003-02-26T00:00:00Z</t>
+          <t>-0218-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>-0216-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q190758</t>
+          <t>http://www.wikidata.org/entity/Q1418062</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Seleucid Empire, Ptolemaic Kingdom</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Q127751</t>
+          <t>Q1195833</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wars of the Roses</t>
+          <t>Jiang Wei's Northern Expeditions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1455-05-22T00:00:00Z</t>
+          <t>0240-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1487-06-16T00:00:00Z</t>
+          <t>0262-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q127751</t>
+          <t>http://www.wikidata.org/entity/Q1195833</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Q28365</t>
+          <t>Q1474893</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lamian War</t>
+          <t>Cleomenean War</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0322-01-01T00:00:00Z</t>
+          <t>-0228-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0321-01-01T00:00:00Z</t>
+          <t>-0221-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q28365</t>
+          <t>http://www.wikidata.org/entity/Q1474893</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sparta, Macedonia, Elis, Achaean League</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Q25857</t>
+          <t>Q146966</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>War of Devolution</t>
+          <t>First Illyro-Roman War</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1667-05-24T00:00:00Z</t>
+          <t>-0228-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1668-05-02T00:00:00Z</t>
+          <t>-0226-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q25857</t>
+          <t>http://www.wikidata.org/entity/Q146966</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Q186336</t>
+          <t>Q76118</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dutch Revolt</t>
+          <t>Third Macedonian War</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1568-01-01T00:00:00Z</t>
+          <t>-0170-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1648-01-01T00:00:00Z</t>
+          <t>-0167-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q186336</t>
+          <t>http://www.wikidata.org/entity/Q76118</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Aetolia, Macedonia, Kingdom of Numidia, Thessaly, Perseus of Macedon, Achaean League, Eumenes II, Lucius Aemilius Paullus Macedonicus, Attalid dynasty, Odrysian kingdom, Ancient Rome, Athamania, Epirus</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Q138107</t>
+          <t>Q34145</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>War of the Sixth Coalition</t>
+          <t>Third Syrian War</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1813-01-01T00:00:00Z</t>
+          <t>-0245-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1814-01-01T00:00:00Z</t>
+          <t>-0240-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q138107</t>
+          <t>http://www.wikidata.org/entity/Q34145</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Seleucid Empire, Ptolemaic Kingdom</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Q26749</t>
+          <t>Q34103</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>War of the Second Coalition</t>
+          <t>Second Syrian War</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1798-06-28T00:00:00Z</t>
+          <t>-0259-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1802-03-25T00:00:00Z</t>
+          <t>-0252-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q26749</t>
+          <t>http://www.wikidata.org/entity/Q34103</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Seleucid Empire, Ptolemaic Kingdom</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Q134949</t>
+          <t>Q75665</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Winter War</t>
+          <t>Second Macedonian War</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1939-11-30T00:00:00Z</t>
+          <t>-0199-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1940-03-13T00:00:00Z</t>
+          <t>-0196-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q134949</t>
+          <t>http://www.wikidata.org/entity/Q75665</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rhodes, Macedonia, Aetolian League, Attalid dynasty, Classical Athens, Ancient Rome, Kingdom of Dardania</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Q37643</t>
+          <t>Q6271</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gulf War</t>
+          <t>Second Punic War</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1990-08-02T00:00:00Z</t>
+          <t>-0217-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1991-02-28T00:00:00Z</t>
+          <t>-0200-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q37643</t>
+          <t>http://www.wikidata.org/entity/Q6271</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Scipio Africanus, Syracuse, Roman Republic, Pergamon, Hannibal, Macedonia, Kingdom of Numidia, Iberians, Aetolian League, Quintus Fabius Maximus Verrucosus, Gaius Terentius Varro, Lucius Aemilius Paullus, Maesulians, Masaesyli, Ancient Carthage, Publius Cornelius Scipio</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Q174904</t>
+          <t>Q75626</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spartan–Persian War</t>
+          <t>First Macedonian War</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0398-01-01T00:00:00Z</t>
+          <t>-0213-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0386-01-01T00:00:00Z</t>
+          <t>-0204-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q174904</t>
+          <t>http://www.wikidata.org/entity/Q75626</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sparta, Macedonia, Achaean League, Aetolian League, Attalid dynasty, list of Illyrians, Messenia, Ancient Rome, Ancient Elis</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Q152218</t>
+          <t>Q6334</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nine Years' War</t>
+          <t>Third Punic War</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1688-09-01T00:00:00Z</t>
+          <t>-0148-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1697-09-01T00:00:00Z</t>
+          <t>-0145-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q152218</t>
+          <t>http://www.wikidata.org/entity/Q6334</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ancient Rome, Ancient Carthage</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Q31944</t>
+          <t>Q6286</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mahdist War</t>
+          <t>First Punic War</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1881-01-01T00:00:00Z</t>
+          <t>-0263-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1899-01-01T00:00:00Z</t>
+          <t>-0240-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q31944</t>
+          <t>http://www.wikidata.org/entity/Q6286</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Roman Republic, Ancient Carthage, tyrant of Syracuse</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Q154697</t>
+          <t>Q714557</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>French and Indian War</t>
+          <t>Kalinga War</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1754-01-01T00:00:00Z</t>
+          <t>-0261-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1763-01-01T00:00:00Z</t>
+          <t>-0260-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q154697</t>
+          <t>http://www.wikidata.org/entity/Q714557</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ashoka, Maurya empire, Kalinga</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Q29269</t>
+          <t>Q936803</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>First Chechen War</t>
+          <t>First Syrian War</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1994-12-11T00:00:00Z</t>
+          <t>-0273-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1996-08-31T00:00:00Z</t>
+          <t>-0270-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q29269</t>
+          <t>http://www.wikidata.org/entity/Q936803</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Seleucid Empire, Ptolemaic Kingdom</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Q6683</t>
+          <t>Q827612</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mexican-American War</t>
+          <t>Jugurthine War</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1846-04-24T00:00:00Z</t>
+          <t>-0110-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1848-02-02T00:00:00Z</t>
+          <t>-0104-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q6683</t>
+          <t>http://www.wikidata.org/entity/Q827612</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Q185729</t>
+          <t>Q933963</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>war on terror</t>
+          <t>Marcomannic Wars</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2001-09-11T00:00:00Z</t>
+          <t>0166-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2021-08-30T00:00:00Z</t>
+          <t>0180-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q185729</t>
+          <t>http://www.wikidata.org/entity/Q933963</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Marcomanni, Quadi, Iazyges, Ancient Rome</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Q26013</t>
+          <t>Q903199</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>War of 1812</t>
+          <t>Cimbrian War</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1812-06-18T00:00:00Z</t>
+          <t>-0112-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1815-02-18T00:00:00Z</t>
+          <t>-0100-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q26013</t>
+          <t>http://www.wikidata.org/entity/Q903199</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Cimbri, Tigurini, Teutons, Ambrones, Ancient Rome</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Q179077</t>
+          <t>Q1006077</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pontiac's War</t>
+          <t>Social War of 220-217 BCE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1763-01-01T00:00:00Z</t>
+          <t>-0219-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1765-01-01T00:00:00Z</t>
+          <t>-0216-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q179077</t>
+          <t>http://www.wikidata.org/entity/Q1006077</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sparta, Macedonia, Boeotia, Achaean League, Aetolian League, Acarnania, Messene, Epirote League, Ancient Elis</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Q51650</t>
+          <t>Q146966</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>People's Crusade</t>
+          <t>First Illyro-Roman War</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1096-04-01T00:00:00Z</t>
+          <t>-0228-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1096-10-01T00:00:00Z</t>
+          <t>-0226-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q51650</t>
+          <t>http://www.wikidata.org/entity/Q146966</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Q146966</t>
+          <t>Q76118</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>First Illyro-Roman War</t>
+          <t>Third Macedonian War</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0228-01-01T00:00:00Z</t>
+          <t>-0170-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-0226-01-01T00:00:00Z</t>
+          <t>-0167-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q146966</t>
+          <t>http://www.wikidata.org/entity/Q76118</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Aetolia, Macedonia, Kingdom of Numidia, Thessaly, Perseus of Macedon, Achaean League, Eumenes II, Lucius Aemilius Paullus Macedonicus, Attalid dynasty, Odrysian kingdom, Ancient Rome, Athamania, Epirus</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Q49100</t>
+          <t>Q34145</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Yom Kippur War</t>
+          <t>Third Syrian War</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1973-10-06T00:00:00Z</t>
+          <t>-0245-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1973-10-26T00:00:00Z</t>
+          <t>-0240-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q49100</t>
+          <t>http://www.wikidata.org/entity/Q34145</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Seleucid Empire, Ptolemaic Kingdom</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Q76118</t>
+          <t>Q34103</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Third Macedonian War</t>
+          <t>Second Syrian War</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-0170-01-01T00:00:00Z</t>
+          <t>-0259-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-0167-01-01T00:00:00Z</t>
+          <t>-0252-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q76118</t>
+          <t>http://www.wikidata.org/entity/Q34103</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Seleucid Empire, Ptolemaic Kingdom</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Q31880</t>
+          <t>Q75665</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Castille War</t>
+          <t>Second Macedonian War</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1578-04-26T00:00:00Z</t>
+          <t>-0199-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1578-07-06T00:00:00Z</t>
+          <t>-0196-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q31880</t>
+          <t>http://www.wikidata.org/entity/Q75665</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rhodes, Macedonia, Aetolian League, Attalid dynasty, Classical Athens, Ancient Rome, Kingdom of Dardania</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Q74109</t>
+          <t>Q6271</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>World War II in Albania</t>
+          <t>Second Punic War</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1939-01-01T00:00:00Z</t>
+          <t>-0217-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1944-01-01T00:00:00Z</t>
+          <t>-0200-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q74109</t>
+          <t>http://www.wikidata.org/entity/Q6271</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Scipio Africanus, Syracuse, Roman Republic, Pergamon, Hannibal, Macedonia, Kingdom of Numidia, Iberians, Aetolian League, Quintus Fabius Maximus Verrucosus, Gaius Terentius Varro, Lucius Aemilius Paullus, Maesulians, Masaesyli, Ancient Carthage, Publius Cornelius Scipio</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Q184183</t>
+          <t>Q75626</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Second Balkan War</t>
+          <t>First Macedonian War</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1913-06-29T00:00:00Z</t>
+          <t>-0213-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1913-08-10T00:00:00Z</t>
+          <t>-0204-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q184183</t>
+          <t>http://www.wikidata.org/entity/Q75626</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Sparta, Macedonia, Achaean League, Aetolian League, Attalid dynasty, list of Illyrians, Messenia, Ancient Rome, Ancient Elis</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Q32929</t>
+          <t>Q6334</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>War of the Austrian Succession</t>
+          <t>Third Punic War</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1740-12-16T00:00:00Z</t>
+          <t>-0148-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1748-10-18T00:00:00Z</t>
+          <t>-0145-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q32929</t>
+          <t>http://www.wikidata.org/entity/Q6334</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ancient Rome, Ancient Carthage</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Q18817</t>
+          <t>Q6286</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>War of the First Coalition</t>
+          <t>First Punic War</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1792-04-20T00:00:00Z</t>
+          <t>-0263-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1797-10-18T00:00:00Z</t>
+          <t>-0240-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q18817</t>
+          <t>http://www.wikidata.org/entity/Q6286</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Roman Republic, Ancient Carthage, tyrant of Syracuse</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Q48883</t>
+          <t>Q1790268</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Goguryeo–Sui War</t>
+          <t>Roman–Parthian War of 161–166</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0598-01-01T00:00:00Z</t>
+          <t>0161-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0614-01-01T00:00:00Z</t>
+          <t>0166-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q48883</t>
+          <t>http://www.wikidata.org/entity/Q1790268</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ancient Rome, Parthian Empire</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Q49103</t>
+          <t>Q2078442</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1982 Lebanon War</t>
+          <t>Second Dacian War</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1982-06-06T00:00:00Z</t>
+          <t>0105-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1985-05-17T00:00:00Z</t>
+          <t>0106-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q49103</t>
+          <t>http://www.wikidata.org/entity/Q2078442</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Roman Empire, Dacia, Roxolani, Iazyges</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Q80330</t>
+          <t>Q1647381</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>English Civil War</t>
+          <t>Third Illyro-Roman War</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1642-01-01T00:00:00Z</t>
+          <t>-0167-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1651-09-03T00:00:00Z</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q80330</t>
+          <t>http://www.wikidata.org/entity/Q1647381</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Q33745</t>
+          <t>Q2073517</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Peloponnesian War</t>
+          <t>War against Nabis</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-0430-01-01T00:00:00Z</t>
+          <t>-0194-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-0403-04-20T00:00:00Z</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q33745</t>
+          <t>http://www.wikidata.org/entity/Q2073517</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Sparta, Pergamon, Rhodes, Macedonia, Achaean League, Aetolian League, Ancient Rome, Argos</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Q31301</t>
+          <t>Q1616064</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Anglo-Turkish War</t>
+          <t>Mithridatic Wars</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1807-01-01T00:00:00Z</t>
+          <t>-0087-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1809-01-01T00:00:00Z</t>
+          <t>-0062-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q31301</t>
+          <t>http://www.wikidata.org/entity/Q1616064</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ancient Rome, Kingdom of Pontus</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Q74623</t>
+          <t>Q1764124</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Great Turkish War</t>
+          <t>Third Mithridatic War</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1683-01-01T00:00:00Z</t>
+          <t>-0072-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1699-01-01T00:00:00Z</t>
+          <t>-0062-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q74623</t>
+          <t>http://www.wikidata.org/entity/Q1764124</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Bosporan Kingdom, Odrysian kingdom, Ancient Rome, Kingdom of Pontus, Kingdom of Cappadocia</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Q151616</t>
+          <t>Q1991765</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Great Northern War</t>
+          <t>Second Mithridatic War</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1700-02-22T00:00:00Z</t>
+          <t>-0082-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1721-09-10T00:00:00Z</t>
+          <t>-0080-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q151616</t>
+          <t>http://www.wikidata.org/entity/Q1991765</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Q46083</t>
+          <t>Q2291971</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Franco-Prussian War</t>
+          <t>Battle of Ilerda</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1870-07-19T00:00:00Z</t>
+          <t>-0048-06-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1871-01-28T00:00:00Z</t>
+          <t>-0048-08-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q46083</t>
+          <t>http://www.wikidata.org/entity/Q2291971</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>populares</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Q168556</t>
+          <t>Q1533828</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Schmalkaldic War</t>
+          <t>Roman–Parthian War of 58–63</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1546-07-20T00:00:00Z</t>
+          <t>0058-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1547-06-02T00:00:00Z</t>
+          <t>0063-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q168556</t>
+          <t>http://www.wikidata.org/entity/Q1533828</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Kingdom of Armenia, Ancient Rome, Parthian Empire</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Q123210</t>
+          <t>Q1647768</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Seventh Russo-Turkish War</t>
+          <t>First Mithridatic War</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1787-08-24T00:00:00Z</t>
+          <t>-0088-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1792-01-09T00:00:00Z</t>
+          <t>-0084-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q123210</t>
+          <t>http://www.wikidata.org/entity/Q1647768</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Q31307</t>
+          <t>Q1790268</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Burmese–Siamese War of 1765–1767</t>
+          <t>Roman–Parthian War of 161–166</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1765-08-23T00:00:00Z</t>
+          <t>0161-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1767-04-07T00:00:00Z</t>
+          <t>0166-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q31307</t>
+          <t>http://www.wikidata.org/entity/Q1790268</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ancient Rome, Parthian Empire</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Q60489</t>
+          <t>Q2078442</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Albanian–Venetian War</t>
+          <t>Second Dacian War</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1447-12-01T00:00:00Z</t>
+          <t>0105-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1448-10-04T00:00:00Z</t>
+          <t>0106-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q60489</t>
+          <t>http://www.wikidata.org/entity/Q2078442</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Roman Empire, Dacia, Roxolani, Iazyges</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Q33143</t>
+          <t>Q1647381</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Seven Years' War</t>
+          <t>Third Illyro-Roman War</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1756-05-17T00:00:00Z</t>
+          <t>-0167-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1763-02-15T00:00:00Z</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q33143</t>
+          <t>http://www.wikidata.org/entity/Q1647381</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Q168442</t>
+          <t>Q2073517</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Anglo-Spanish War of 1625–1630</t>
+          <t>War against Nabis</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1625-11-01T00:00:00Z</t>
+          <t>-0194-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1630-11-15T00:00:00Z</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q168442</t>
+          <t>http://www.wikidata.org/entity/Q2073517</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Sparta, Pergamon, Rhodes, Macedonia, Achaean League, Aetolian League, Ancient Rome, Argos</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Q154940</t>
+          <t>Q1616064</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lapland War</t>
+          <t>Mithridatic Wars</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1944-09-15T00:00:00Z</t>
+          <t>-0087-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1945-04-25T00:00:00Z</t>
+          <t>-0062-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q154940</t>
+          <t>http://www.wikidata.org/entity/Q1616064</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ancient Rome, Kingdom of Pontus</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Q122100</t>
+          <t>Q1764124</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Continuation War</t>
+          <t>Third Mithridatic War</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1941-06-25T00:00:00Z</t>
+          <t>-0072-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1944-09-19T00:00:00Z</t>
+          <t>-0062-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q122100</t>
+          <t>http://www.wikidata.org/entity/Q1764124</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Bosporan Kingdom, Odrysian kingdom, Ancient Rome, Kingdom of Pontus, Kingdom of Cappadocia</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Q186284</t>
+          <t>Q1991765</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Polish–Soviet War</t>
+          <t>Second Mithridatic War</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1919-02-01T00:00:00Z</t>
+          <t>-0082-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1921-03-01T00:00:00Z</t>
+          <t>-0080-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q186284</t>
+          <t>http://www.wikidata.org/entity/Q1991765</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Q153650</t>
+          <t>Q2291971</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Austro-Prussian War</t>
+          <t>Battle of Ilerda</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1866-06-14T00:00:00Z</t>
+          <t>-0048-06-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1866-07-26T00:00:00Z</t>
+          <t>-0048-08-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q153650</t>
+          <t>http://www.wikidata.org/entity/Q2291971</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>populares</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Q82664</t>
+          <t>Q1533828</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Iran–Iraq War</t>
+          <t>Roman–Parthian War of 58–63</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1980-09-22T00:00:00Z</t>
+          <t>0058-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1988-08-20T00:00:00Z</t>
+          <t>0063-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q82664</t>
+          <t>http://www.wikidata.org/entity/Q1533828</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kingdom of Armenia, Ancient Rome, Parthian Empire</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Q49092</t>
+          <t>Q1647768</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1948 Arab–Israeli War</t>
+          <t>First Mithridatic War</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1948-05-15T00:00:00Z</t>
+          <t>-0088-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1949-03-10T00:00:00Z</t>
+          <t>-0084-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q49092</t>
+          <t>http://www.wikidata.org/entity/Q1647768</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Q49101</t>
+          <t>Q1790268</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Suez Crisis</t>
+          <t>Roman–Parthian War of 161–166</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1956-10-29T00:00:00Z</t>
+          <t>0161-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1956-11-07T00:00:00Z</t>
+          <t>0166-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q49101</t>
+          <t>http://www.wikidata.org/entity/Q1790268</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Ancient Rome, Parthian Empire</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Q129864</t>
+          <t>Q2078442</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Indian Mutiny of 1857</t>
+          <t>Second Dacian War</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1857-05-10T00:00:00Z</t>
+          <t>0105-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1858-06-20T00:00:00Z</t>
+          <t>0106-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q129864</t>
+          <t>http://www.wikidata.org/entity/Q2078442</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Roman Empire, Dacia, Roxolani, Iazyges</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Q170682</t>
+          <t>Q1647381</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gaza War (2008–2009)</t>
+          <t>Third Illyro-Roman War</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2008-12-27T00:00:00Z</t>
+          <t>-0167-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2009-01-18T00:00:00Z</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q170682</t>
+          <t>http://www.wikidata.org/entity/Q1647381</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Q34145</t>
+          <t>Q2073517</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Third Syrian War</t>
+          <t>War against Nabis</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>-0245-01-01T00:00:00Z</t>
+          <t>-0194-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-0240-01-01T00:00:00Z</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q34145</t>
+          <t>http://www.wikidata.org/entity/Q2073517</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Sparta, Pergamon, Rhodes, Macedonia, Achaean League, Aetolian League, Ancient Rome, Argos</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Q34103</t>
+          <t>Q1616064</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Second Syrian War</t>
+          <t>Mithridatic Wars</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>-0259-01-01T00:00:00Z</t>
+          <t>-0087-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-0252-01-01T00:00:00Z</t>
+          <t>-0062-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q34103</t>
+          <t>http://www.wikidata.org/entity/Q1616064</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Ancient Rome, Kingdom of Pontus</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Q123070</t>
+          <t>Q1764124</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sixth Russo-Turkish War</t>
+          <t>Third Mithridatic War</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1768-01-01T00:00:00Z</t>
+          <t>-0072-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1774-01-01T00:00:00Z</t>
+          <t>-0062-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q123070</t>
+          <t>http://www.wikidata.org/entity/Q1764124</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Bosporan Kingdom, Odrysian kingdom, Ancient Rome, Kingdom of Pontus, Kingdom of Cappadocia</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Q159950</t>
+          <t>Q1991765</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Russo-Japanese War</t>
+          <t>Second Mithridatic War</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1904-02-08T00:00:00Z</t>
+          <t>-0082-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1905-09-05T00:00:00Z</t>
+          <t>-0080-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q159950</t>
+          <t>http://www.wikidata.org/entity/Q1991765</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Q49097</t>
+          <t>Q2291971</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1948 Palestine war</t>
+          <t>Battle of Ilerda</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1947-11-30T00:00:00Z</t>
+          <t>-0048-06-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1949-07-20T00:00:00Z</t>
+          <t>-0048-08-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q49097</t>
+          <t>http://www.wikidata.org/entity/Q2291971</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>populares</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Q75665</t>
+          <t>Q1533828</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Second Macedonian War</t>
+          <t>Roman–Parthian War of 58–63</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>-0199-01-01T00:00:00Z</t>
+          <t>0058-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-0196-01-01T00:00:00Z</t>
+          <t>0063-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q75665</t>
+          <t>http://www.wikidata.org/entity/Q1533828</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Kingdom of Armenia, Ancient Rome, Parthian Empire</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Q8663</t>
+          <t>Q1647768</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Korean War</t>
+          <t>First Mithridatic War</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1950-06-25T00:00:00Z</t>
+          <t>-0088-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1953-07-27T00:00:00Z</t>
+          <t>-0084-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q8663</t>
+          <t>http://www.wikidata.org/entity/Q1647768</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Q177918</t>
+          <t>Q110064418</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>First Balkan War</t>
+          <t>Bellum Octavianum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1912-10-08T00:00:00Z</t>
+          <t>-0086-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1913-05-30T00:00:00Z</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q177918</t>
+          <t>http://www.wikidata.org/entity/Q110064418</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Q158677</t>
+          <t>Q91338125</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Northern Seven Years' War</t>
+          <t>Seleucid Civil War of 128–125 BCE</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1563-01-01T00:00:00Z</t>
+          <t>-0127-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1570-01-01T00:00:00Z</t>
+          <t>-0124-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q158677</t>
+          <t>http://www.wikidata.org/entity/Q91338125</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Demetrius II Nicator, Alexandros II Zabinas</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Q74298</t>
+          <t>Q90673916</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Polish–Ottoman War of 1672–1676</t>
+          <t>Seleucid Civil War of 147–137 BCE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1672-01-01T00:00:00Z</t>
+          <t>-0146-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1676-01-01T00:00:00Z</t>
+          <t>-0136-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q74298</t>
+          <t>http://www.wikidata.org/entity/Q90673916</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Antiochus VII Sidetes, Diodotus Tryphon, Alexander Balas, Antiochus VI Dionysus, Demetrius II Nicator</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Q179250</t>
+          <t>Q90673853</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>French invasion of Russia</t>
+          <t>Seleucid Civil War of 152–150 BCE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1812-06-24T00:00:00Z</t>
+          <t>-0151-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1812-12-14T00:00:00Z</t>
+          <t>-0149-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q179250</t>
+          <t>http://www.wikidata.org/entity/Q90673853</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Demetrius I Soter, Alexander Balas</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Q75756</t>
+          <t>Q91562491</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Second Congo War</t>
+          <t>Seleucid Civil War of 124–123 BCE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1998-08-02T00:00:00Z</t>
+          <t>-0123-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2003-06-30T00:00:00Z</t>
+          <t>-0122-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q75756</t>
+          <t>http://www.wikidata.org/entity/Q91562491</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Cleopatra Thea, Antiochus VIII Grypus, Alexandros II Zabinas</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Q58947</t>
+          <t>Q85772264</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Paraguayan War</t>
+          <t>Judean Civil War</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1864-12-27T00:00:00Z</t>
+          <t>-0092-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1870-03-01T00:00:00Z</t>
+          <t>-0086-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q58947</t>
+          <t>http://www.wikidata.org/entity/Q85772264</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Q6271</t>
+          <t>Q42044165</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Second Punic War</t>
+          <t>War of the Brothers</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>-0217-01-01T00:00:00Z</t>
+          <t>-0238-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-0200-01-01T00:00:00Z</t>
+          <t>-0235-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q6271</t>
+          <t>http://www.wikidata.org/entity/Q42044165</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Q48249</t>
+          <t>Q97278920</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Falklands War</t>
+          <t>War of the Seleucid Succession of 114–84 BCE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1982-04-02T00:00:00Z</t>
+          <t>-0113-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1982-06-14T00:00:00Z</t>
+          <t>-0083-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q48249</t>
+          <t>http://www.wikidata.org/entity/Q97278920</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Q75626</t>
+          <t>Q751743</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>First Macedonian War</t>
+          <t>Yellow Turban Rebellion</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>-0213-01-01T00:00:00Z</t>
+          <t>0184-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-0204-01-01T00:00:00Z</t>
+          <t>0205-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q75626</t>
+          <t>http://www.wikidata.org/entity/Q751743</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Eastern Han, Yellow Turban Army</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Q12583</t>
+          <t>Q135448093</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Spanish–American War</t>
+          <t>War of the Armenian Succession</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1898-04-25T00:00:00Z</t>
+          <t>-0200-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1898-08-11T00:00:00Z</t>
+          <t>-0199-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q12583</t>
+          <t>http://www.wikidata.org/entity/Q135448093</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Seleucid Empire, Kingdom of Armenia, Kingdom of Sophene</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Q6334</t>
+          <t>Q97186916</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Third Punic War</t>
+          <t>War of the Seleucid Succession 152–137 BCE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>-0148-01-01T00:00:00Z</t>
+          <t>-0151-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-0145-01-01T00:00:00Z</t>
+          <t>-0136-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q6334</t>
+          <t>http://www.wikidata.org/entity/Q97186916</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Q165136</t>
+          <t>Q97278928</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Swabian War</t>
+          <t>War of the Seleucid Succession 128–123 BCE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1499-02-01T00:00:00Z</t>
+          <t>-0127-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1499-10-01T00:00:00Z</t>
+          <t>-0122-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q165136</t>
+          <t>http://www.wikidata.org/entity/Q97278928</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Q170314</t>
+          <t>Q131686578</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Second Sino-Japanese War</t>
+          <t>Dardanian-Celtic War</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1937-07-07T00:00:00Z</t>
+          <t>-0278-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1945-09-09T00:00:00Z</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q170314</t>
+          <t>http://www.wikidata.org/entity/Q131686578</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Ancient Celts, Kingdom of Dardania</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Q163476</t>
+          <t>Q132068862</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ottoman–Safavid War</t>
+          <t>Epirote-Macedonian War</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1623-01-01T00:00:00Z</t>
+          <t>-0288-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1639-01-01T00:00:00Z</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q163476</t>
+          <t>http://www.wikidata.org/entity/Q132068862</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Macedonia, Aetolian League, Epirus</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Q74302</t>
+          <t>Q131686212</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Polish–Ottoman War of 1633–34</t>
+          <t>Himyarite-Axumite War</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1633-01-01T00:00:00Z</t>
+          <t>0270-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1634-01-01T00:00:00Z</t>
+          <t>0272-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q74302</t>
+          <t>http://www.wikidata.org/entity/Q131686212</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Kingdom of Aksum, Himyarite kingdom</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Q154981</t>
+          <t>Q2556352</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Second Schleswig War</t>
+          <t>Galatian War</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1864-02-01T00:00:00Z</t>
+          <t>-0188-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1864-10-31T00:00:00Z</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q154981</t>
+          <t>http://www.wikidata.org/entity/Q2556352</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Ancient Rome, Kingdom of Pergamon, Galatians</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Q47985</t>
+          <t>Q2367618</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Rus'–Byzantine War of 1043</t>
+          <t>Pannonian War</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>-0013-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>-0009-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q47985</t>
+          <t>http://www.wikidata.org/entity/Q2367618</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Q166001</t>
+          <t>Q2345065</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Scanian War</t>
+          <t>Second Illyro-Roman War</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1675-01-01T00:00:00Z</t>
+          <t>-0219-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1679-01-01T00:00:00Z</t>
+          <t>-0218-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q166001</t>
+          <t>http://www.wikidata.org/entity/Q2345065</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Q120843</t>
+          <t>Q2338771</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Second Chechen War</t>
+          <t>Cretan War of 205-200 BCE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1999-08-26T00:00:00Z</t>
+          <t>-0204-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2009-04-16T00:00:00Z</t>
+          <t>-0199-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q120843</t>
+          <t>http://www.wikidata.org/entity/Q2338771</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Athens, Sparta, Pergamon, Byzantium, Rhodes, Macedonia, Knossos, Aetolian League, Acarnania, Cyzicus, Ierapetra, Olous</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Q189266</t>
+          <t>Q2619223</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Eastern Front</t>
+          <t>Aetolian War</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>1941-06-22T00:00:00Z</t>
+          <t>-0190-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1955-01-21T00:00:00Z</t>
+          <t>-0188-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q189266</t>
+          <t>http://www.wikidata.org/entity/Q2619223</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Macedonia, Achaean League, Aetolian League, Athamanians, Ancient Rome</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Q94916</t>
+          <t>Q2986801</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Second Italo-Ethiopian War</t>
+          <t>Qin's Wars of Unification</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1935-10-03T00:00:00Z</t>
+          <t>-0229-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1937-02-19T00:00:00Z</t>
+          <t>-0220-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q94916</t>
+          <t>http://www.wikidata.org/entity/Q2986801</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Qin, Zhao, Chu, Qi, Wei, Yan, Han</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Q179275</t>
+          <t>Q2334699</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>insurgency in Khyber Pakhtunkhwa</t>
+          <t>Antony's Parthian War</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2004-03-16T00:00:00Z</t>
+          <t>-0035-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2684,443 +3029,3506 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q179275</t>
+          <t>http://www.wikidata.org/entity/Q2334699</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Roman Republic, Parthian Empire</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Q68969</t>
+          <t>Q2583092</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Croatian War of Independence</t>
+          <t>Liberators' Civil War</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1991-03-31T00:00:00Z</t>
+          <t>-0042-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1995-08-07T00:00:00Z</t>
+          <t>-0041-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q68969</t>
+          <t>http://www.wikidata.org/entity/Q2583092</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Q178687</t>
+          <t>Q770951</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>First Sino-Japanese War</t>
+          <t>War of the Eight Princes</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1894-08-01T00:00:00Z</t>
+          <t>0291-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1895-04-17T00:00:00Z</t>
+          <t>0306-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q178687</t>
+          <t>http://www.wikidata.org/entity/Q770951</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Sima Lun, Sima Ying, Sima Yue, Sima Yong, Sima Jiong, Sima Liang, Sima Wei, Sima Ai</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Q182865</t>
+          <t>Q1238338</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>War in Afghanistan (2001–2021)</t>
+          <t>Caesar's Civil War</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2001-10-07T00:00:00Z</t>
+          <t>-0048-01-08T00:00:00Z</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2021-08-30T00:00:00Z</t>
+          <t>-0044-03-15T00:00:00Z</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q182865</t>
+          <t>http://www.wikidata.org/entity/Q1238338</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Q6286</t>
+          <t>Q1588511</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>First Punic War</t>
+          <t>Hasmonean Civil War</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>-0263-01-01T00:00:00Z</t>
+          <t>-0066-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-0240-01-01T00:00:00Z</t>
+          <t>-0062-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q6286</t>
+          <t>http://www.wikidata.org/entity/Q1588511</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Pompey, Antipater the Idumaean, Aristobulus II, Hyrcanus II, Marcus Aemilius Scaurus, Aretas III</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Q189266</t>
+          <t>Q2116320</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Eastern Front</t>
+          <t>Final War of the Roman Republic</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1941-06-22T00:00:00Z</t>
+          <t>-0031-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1945-05-07T00:00:00Z</t>
+          <t>-0029-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q189266</t>
+          <t>http://www.wikidata.org/entity/Q2116320</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Q151663</t>
+          <t>Q741777</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Revolt of the Comuneros</t>
+          <t>War of Mutina</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1520-01-01T00:00:00Z</t>
+          <t>-0043-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1522-01-01T00:00:00Z</t>
+          <t>-0041-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q151663</t>
+          <t>http://www.wikidata.org/entity/Q741777</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Mark Antony, Ancient Rome</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Q152004</t>
+          <t>Q2730371</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>War of the Pacific</t>
+          <t>Bellum Siculum</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>1879-04-05T00:00:00Z</t>
+          <t>-0041-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>1884-04-04T00:00:00Z</t>
+          <t>-0035-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q152004</t>
+          <t>http://www.wikidata.org/entity/Q2730371</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Q54434</t>
+          <t>Q97278920</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>War of Jenkins' Ear</t>
+          <t>War of the Seleucid Succession of 114–84 BCE</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1739-10-22T00:00:00Z</t>
+          <t>-0113-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1748-10-18T00:00:00Z</t>
+          <t>-0083-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q54434</t>
+          <t>http://www.wikidata.org/entity/Q97278920</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Q157548</t>
+          <t>Q751743</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>War of the Bavarian Succession</t>
+          <t>Yellow Turban Rebellion</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1778-07-03T00:00:00Z</t>
+          <t>0184-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1779-05-13T00:00:00Z</t>
+          <t>0205-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q157548</t>
+          <t>http://www.wikidata.org/entity/Q751743</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Eastern Han, Yellow Turban Army</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Q49104</t>
+          <t>Q135448093</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2006 Lebanon War</t>
+          <t>War of the Armenian Succession</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2006-07-12T00:00:00Z</t>
+          <t>-0200-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2006-08-14T00:00:00Z</t>
+          <t>-0199-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q49104</t>
+          <t>http://www.wikidata.org/entity/Q135448093</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Seleucid Empire, Kingdom of Armenia, Kingdom of Sophene</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Q163270</t>
+          <t>Q97186916</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Second Thirty Years' War</t>
+          <t>War of the Seleucid Succession 152–137 BCE</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1914-01-01T00:00:00Z</t>
+          <t>-0151-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1945-01-01T00:00:00Z</t>
+          <t>-0136-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q163270</t>
+          <t>http://www.wikidata.org/entity/Q97186916</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Q12551</t>
+          <t>Q97278928</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hundred Years' War</t>
+          <t>War of the Seleucid Succession 128–123 BCE</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1337-06-01T00:00:00Z</t>
+          <t>-0127-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1453-10-18T00:00:00Z</t>
+          <t>-0122-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q12551</t>
+          <t>http://www.wikidata.org/entity/Q97278928</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Q83085</t>
+          <t>Q28701147</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Soviet-Afghan War</t>
+          <t>Anti-Terrorist Operation in Ukraine</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>1979-12-25T00:00:00Z</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1989-02-15T00:00:00Z</t>
+          <t>2018-04-30T00:00:00Z</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q83085</t>
+          <t>http://www.wikidata.org/entity/Q28701147</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Q172068</t>
+          <t>Q1340107</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>World War II in Yugoslav Macedonia</t>
+          <t>Cantabrian Wars</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>1941-10-11T00:00:00Z</t>
+          <t>-0028-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>1944-11-23T00:00:00Z</t>
+          <t>-0018-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q172068</t>
+          <t>http://www.wikidata.org/entity/Q1340107</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Roman Empire, Cantabri, Astures</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Q87138</t>
+          <t>Q1192043</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Greco-Turkish War</t>
+          <t>Roman–Parthian Wars</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1919-05-15T00:00:00Z</t>
+          <t>-0065-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1922-10-11T00:00:00Z</t>
+          <t>0217-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q87138</t>
+          <t>http://www.wikidata.org/entity/Q1192043</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Kingdom of Iberia, Galatia, Judea, Kingdom of Armenia, Osroene, Atropatene, Kingdom of Commagene, Sophene, Ancient Rome, Parthian Empire, Kingdom of Chalcis, Kingdom of Araba, Kingdom of Pontus, Nabataean kingdom, Kingdom of Cappadocia</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Q49077</t>
+          <t>Q723608</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Six-Day War</t>
+          <t>Trajan's Dacian Wars</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1967-06-05T00:00:00Z</t>
+          <t>0101-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1967-06-10T00:00:00Z</t>
+          <t>0106-01-01T00:00:00Z</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q49077</t>
+          <t>http://www.wikidata.org/entity/Q723608</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Roman Empire, Dacia</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Q744969</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Han–Xiongnu Wars</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>-0138-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>0089-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q744969</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Han dynasty, Xiongnu</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Q1202928</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Lusitanian War</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>-0154-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>-0138-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q1202928</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Roman Republic, Lusitanians</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Q75813</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Macedonian Wars</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>-0213-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>-0147-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q75813</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Ancient Rome</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Q1330607</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Syrian Wars</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>-0273-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>-0167-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q1330607</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Seleucid Empire, Diadochi, Ptolemaic Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Q596373</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Pyrrhic War</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>-0279-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>-0274-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q596373</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Carthage, Taranto, Aetolia, Thessaly, Umbri, Acarnania, Samnites, Athamanians, Paeligni, Bruttii, Marrucini, Daunians, Lucanians, Marsi, Ancient Rome, Frentani, Epirus</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Q124988</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Punic Wars</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>-0263-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>-0145-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q124988</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Roman Republic, Ancient Carthage</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Q500409</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Roman–Persian Wars</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>-0053-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>0628-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q500409</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Byzantine Empire, Sasanian Empire, Ancient Rome, Parthian Empire</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Q154552</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Illyro-Roman Wars</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>0229-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>0167-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q154552</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Q2583092</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Liberators' Civil War</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>-0042-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>-0041-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q2583092</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Q770951</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>War of the Eight Princes</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>0291-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>0306-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q770951</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Sima Lun, Sima Ying, Sima Yue, Sima Yong, Sima Jiong, Sima Liang, Sima Wei, Sima Ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Q1238338</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Caesar's Civil War</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>-0048-01-08T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>-0044-03-15T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q1238338</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Q1588511</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Hasmonean Civil War</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>-0066-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>-0062-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q1588511</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Pompey, Antipater the Idumaean, Aristobulus II, Hyrcanus II, Marcus Aemilius Scaurus, Aretas III</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Q2116320</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Final War of the Roman Republic</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>-0031-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>-0029-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q2116320</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Q741777</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>War of Mutina</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>-0043-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>-0041-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q741777</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Mark Antony, Ancient Rome</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Q2730371</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Bellum Siculum</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>-0041-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>-0035-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q2730371</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Q3984897</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Third Samnite War</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>-0297-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>-0289-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q3984897</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Samnites, Ancient Rome</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Q3651751</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Trajan's Parthian campaign</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0115-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>0117-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q3651751</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Kingdom of Armenia, Ancient Rome, Parthian Empire</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Q3778702</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Pompey's Jewish War</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>-0073-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>-0062-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q3778702</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Roman Republic, Hasmonean Judea</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Q3651748</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Parthian War of Caracalla</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>0216-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>0217-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q3651748</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Roman Empire, Parthian Empire</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Q3118998</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>War against Lyctus</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>-0220-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>-0218-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q3118998</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Rhodes, Macedonia, Knossos, Achaean League, Aetolian League, Lyctus, Gortyn, Kydonia, Lappei Municipal Unit, Polyrrhenia</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Q3401862</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Wars between Rome and the Veii</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>-0395-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q3401862</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Veii, Ancient Rome</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Q110064418</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Bellum Octavianum</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>-0086-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q110064418</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Q91338125</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Seleucid Civil War of 128–125 BCE</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>-0127-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>-0124-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q91338125</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Demetrius II Nicator, Alexandros II Zabinas</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Q90673916</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Seleucid Civil War of 147–137 BCE</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>-0146-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>-0136-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q90673916</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Antiochus VII Sidetes, Diodotus Tryphon, Alexander Balas, Antiochus VI Dionysus, Demetrius II Nicator</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Q90673853</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Seleucid Civil War of 152–150 BCE</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>-0151-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>-0149-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q90673853</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Demetrius I Soter, Alexander Balas</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Q91562491</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Seleucid Civil War of 124–123 BCE</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>-0123-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>-0122-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q91562491</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Cleopatra Thea, Antiochus VIII Grypus, Alexandros II Zabinas</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Q85772264</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Judean Civil War</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>-0092-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>-0086-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q85772264</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Q42044165</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>War of the Brothers</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>-0238-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>-0235-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q42044165</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Q135937294</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Armenian–Parthian War</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>-0093-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>-0091-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q135937294</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Kingdom of Armenia, Parthian Empire</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Q137217360</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Bellum Dardanicum</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>-0074-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>-0072-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q137217360</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Roman Republic, Dardani</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Q243721</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Year of the Five Emperors</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>0193-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q243721</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Q470596</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Year of the Four Emperors</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>0069-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q470596</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Q4793354</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Armenian–Parthian War</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>-0086-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>-0084-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q4793354</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Corduene, Kingdom of Armenia, Parthian Empire</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Q4207759</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Seleucid–Parthian Wars</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>-0237-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>-0128-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q4207759</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Seleucid Empire, Parthian Empire</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Q4349810</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>First Dacian War</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>0101-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>0102-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q4349810</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Roman Empire, Dacia</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Q55644383</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Roman–Greek wars</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>-0279-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>-0029-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q55644383</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Q123990089</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Sasanian–Kushan Wars</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>0270-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>0370-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q123990089</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Kushan Empire, Sasanian Empire</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Q137640001</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Domitian's Wars against the Chatti</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>0083-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>0089-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q137640001</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Roman Empire, Chatti, Cherusci, Hermunduri, Romans</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Q137719648</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Roman–Dardanian wars</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>-0096-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>-0027-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q137719648</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Roman Republic, Maedi, Kingdom of Dardania</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Q3778726</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Sertorian War</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>-0079-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>-0071-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q3778726</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Kingdom of Mauretania, Iberians, populares, optimates, Cilician pirates, Celtiberians</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Q5124705</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Civil War of Wa</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>0200-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q5124705</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Yamatai</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Q3778747</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Bagaudic Wars</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>0280-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>0460-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q3778747</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Roman Empire, Bagaudae</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Q137640001</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Domitian's Wars against the Chatti</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>0083-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>0089-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q137640001</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Roman Empire, Chatti, Cherusci, Hermunduri, Romans</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Q137719648</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Roman–Dardanian wars</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>-0096-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>-0027-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q137719648</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Roman Republic, Maedi, Kingdom of Dardania</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Q7968690</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>War of the Heavenly Horses</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>-0103-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>-0100-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q7968690</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Q9377266</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Alexandrian War</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>-0047-08-30T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>-0047-12-30T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q9377266</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Ancient Rome, Ptolemaic Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Q7968589</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Iberian–Armenian War</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>0050-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>0053-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q7968589</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Roman Empire, Kingdom of Iberia, Kingdom of Armenia, Parthian Empire</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Q16327601</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Demetrius War</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>-0238-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>-0228-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q16327601</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Macedonia, Achaean League, Aetolian League</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Q16178616</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Second Judeo–Seleucid War</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>-0164-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>-0161-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q16178616</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Seleucid Empire, Maccabees</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Q11893060</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Roman–Parthian War of 195–198</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>0195-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>0198-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q11893060</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Ancient Rome, Parthian Empire</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Q11924841</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Gothic War of 248–253</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>0248-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>0253-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q11924841</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Ancient Rome</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Q12277247</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Gothic War of 267–269</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>0267-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>0269-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q12277247</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Q30913411</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Fifth War of the Diadochi</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>-0287-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>-0285-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q30913411</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Q30671673</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Second Celtiberian War</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>-0153-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>-0150-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q30671673</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Roman Republic, Celtiberians</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Q97198039</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Greco-Ardiaean War</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>-0230-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>-0228-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97198039</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Q97187081</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Cretan War of 155–153 BCE</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>-0154-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>-0152-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97187081</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Q55630237</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Pompeian–Parthian Invasion of 40 BCE</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>-0039-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>-0037-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q55630237</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Judea, Kingdom of Commagene, Ancient Rome, Parthian Empire</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Q97305706</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>War of Byzantium against Bithynia and Rhodes</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>-0300-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97305706</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Byzantium, Rhodes, Kingdom of Bithynia</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Q97306131</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>War between Antiochus I Soter and the Northern League</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>-0300-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97306131</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Byzantium, Seleucid Empire, Heraclea Pontica, Chalcedon</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Q97279607</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Bithynian-Pergamene War of 186–183 BCE</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>-0185-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>-0182-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97279607</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Kingdom of Pergamon, Kingdom of Bithynia, Galatians</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Q97305923</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Aetolian-Boeotian War</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>-0244-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-0244-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97305923</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Aetolian League, Boeotian confederation</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Q97185211</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Bithynian-Pergamene War of 156–154 BCE</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>-0155-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>-0153-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97185211</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Rhodes, Kingdom of Pergamon, Kingdom of Bithynia, Kingdom of Pontus, Kingdom of Cappadocia</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Q97186969</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>War between Rhodes and Kaunos</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>-0200-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97186969</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Rhodes, Kaunos, Calynda</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Q97278952</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>War between Apollonia and Mesembria</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>-0200-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97278952</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Apollonia Pontica, Histria, Mesembria</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Q19716429</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Fourth Samnite War</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>-0281-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>-0271-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q19716429</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Samnites, Ancient Rome</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Q18408280</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Pontic War</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>-0047-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>-0046-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q18408280</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Roman Republic, Galatia, Kingdom of Pontus, Kingdom of Cappadocia</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Q28963610</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Struggle over Macedon</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>-0297-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>-0284-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q28963610</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Ptolemaic dynasty, Antigonid dynasty, Antipatrid dynasty</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Q28963669</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>War of Lysimachus and Seleucus</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>-0284-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>-0280-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q28963669</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Ptolemaic dynasty, Antigonid dynasty, Antipatrid dynasty</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Q24067626</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>War in Yugoslavia during World War II</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>1945-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q24067626</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Q51180267</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Roman-Dalmatae Wars</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>-0155-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0009-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q51180267</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Q27962835</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Roman–Bosporan War</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>0045-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>0049-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q27962835</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Bosporan Kingdom, Aorsi, Ancient Rome, Siraces</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Q30913409</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Sixth War of the Diadochi</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>-0281-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>-0280-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q30913409</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Q30913411</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Fifth War of the Diadochi</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>-0287-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>-0285-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q30913411</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Q30671673</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Second Celtiberian War</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>-0153-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>-0150-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q30671673</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Roman Republic, Celtiberians</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Q97198039</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Greco-Ardiaean War</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>-0230-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>-0228-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97198039</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Q97187081</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Cretan War of 155–153 BCE</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>-0154-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>-0152-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97187081</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Q55630237</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Pompeian–Parthian Invasion of 40 BCE</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>-0039-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>-0037-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q55630237</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Judea, Kingdom of Commagene, Ancient Rome, Parthian Empire</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Q97305706</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>War of Byzantium against Bithynia and Rhodes</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>-0300-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97305706</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Byzantium, Rhodes, Kingdom of Bithynia</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Q97306131</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>War between Antiochus I Soter and the Northern League</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>-0300-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97306131</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Byzantium, Seleucid Empire, Heraclea Pontica, Chalcedon</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Q97279607</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Bithynian-Pergamene War of 186–183 BCE</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>-0185-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>-0182-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97279607</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Kingdom of Pergamon, Kingdom of Bithynia, Galatians</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Q97305923</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Aetolian-Boeotian War</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>-0244-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>-0244-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97305923</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Aetolian League, Boeotian confederation</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Q97185211</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Bithynian-Pergamene War of 156–154 BCE</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>-0155-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>-0153-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97185211</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Rhodes, Kingdom of Pergamon, Kingdom of Bithynia, Kingdom of Pontus, Kingdom of Cappadocia</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Q97186969</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>War between Rhodes and Kaunos</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>-0200-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97186969</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Rhodes, Kaunos, Calynda</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Q97278952</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>War between Apollonia and Mesembria</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>-0200-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97278952</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Apollonia Pontica, Histria, Mesembria</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Q65052293</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Parthian–Greco Bactrian War</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>-0155-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q65052293</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Greco-Bactrian Kingdom, Parthian Empire</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Q97306148</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Carian War</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>-0279-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>-0278-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97306148</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Seleucid Empire, Ptolemaic Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Q97186053</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Pontic-Pergamene War</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>-0182-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>-0178-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97186053</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Rhodes, Kingdom of Pergamon, Kingdom of Bithynia, Kingdom of Pontus, Galatians, Kingdom of Cappadocia</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Q97178295</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Greco-Carthaginian War</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>-0279-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>-0274-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97178295</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Q97305915</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>War between the Achaean League and Macedonia</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>-0242-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>-0228-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97305915</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Q97199785</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Seleucid-Pergamene War</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>-0229-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>-0215-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q97199785</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Seleucid Empire, Kingdom of Pergamon</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Q60745019</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Dardanian-Bastarnae War</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>-0178-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>-0174-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q60745019</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Bastarnae, Kingdom of Dardania</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Q486831</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Roman–Seleucid War</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>-0191-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>-0187-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q486831</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Pergamon, Rhodes, Macedonia, Seleucid Empire, Cappadocia, Achaean League, Aetolian League, Athamanians, Ancient Rome</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Q1076902</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Chremonidean War</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>-0266-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>-0260-01-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q1076902</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Sparta, Ptolemy II Philadelphus, Macedonia, Antigonus II Gonatas, Areus I, Patroclus, Classical Athens, Chremonides, Ptolemaic Kingdom</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>